--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/156.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/156.xlsx
@@ -426,13 +426,13 @@
         <v>-5.337180197714765</v>
       </c>
       <c r="E2">
-        <v>-10.24248194488638</v>
+        <v>-9.865359686475607</v>
       </c>
       <c r="F2">
-        <v>-3.062061982854319</v>
+        <v>-3.254541640552041</v>
       </c>
       <c r="G2">
-        <v>-7.860557168568302</v>
+        <v>-7.294139379526698</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-5.219388813579957</v>
       </c>
       <c r="E3">
-        <v>-10.89689172373482</v>
+        <v>-9.442825890715916</v>
       </c>
       <c r="F3">
-        <v>-2.986159709445053</v>
+        <v>-3.634843276850177</v>
       </c>
       <c r="G3">
-        <v>-7.651284342848812</v>
+        <v>-6.706474509214051</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-5.010887858639903</v>
       </c>
       <c r="E4">
-        <v>-11.38036519421573</v>
+        <v>-9.617896695852451</v>
       </c>
       <c r="F4">
-        <v>-2.744576457986173</v>
+        <v>-3.223223064221268</v>
       </c>
       <c r="G4">
-        <v>-8.043855453986668</v>
+        <v>-6.43384446296399</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-4.695324477181212</v>
       </c>
       <c r="E5">
-        <v>-11.87427679728432</v>
+        <v>-10.98874729050641</v>
       </c>
       <c r="F5">
-        <v>-2.985987877353228</v>
+        <v>-3.093565852777198</v>
       </c>
       <c r="G5">
-        <v>-7.146326831743778</v>
+        <v>-7.026822758867167</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-4.237859118197203</v>
       </c>
       <c r="E6">
-        <v>-12.13960461786774</v>
+        <v>-11.21892962431629</v>
       </c>
       <c r="F6">
-        <v>-2.760537046201972</v>
+        <v>-3.022337887377351</v>
       </c>
       <c r="G6">
-        <v>-6.946273875351159</v>
+        <v>-6.964978457648042</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-3.625304982247074</v>
       </c>
       <c r="E7">
-        <v>-13.16046757036488</v>
+        <v>-11.81705047124939</v>
       </c>
       <c r="F7">
-        <v>-2.79618389079964</v>
+        <v>-2.982872727817558</v>
       </c>
       <c r="G7">
-        <v>-7.267952964311062</v>
+        <v>-6.897016268272344</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-2.846414005818681</v>
       </c>
       <c r="E8">
-        <v>-12.82736207930866</v>
+        <v>-12.46716725673856</v>
       </c>
       <c r="F8">
-        <v>-2.568917340816334</v>
+        <v>-3.515497574621533</v>
       </c>
       <c r="G8">
-        <v>-6.885968977807796</v>
+        <v>-6.369371588586684</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-1.915847395804273</v>
       </c>
       <c r="E9">
-        <v>-14.31953049262811</v>
+        <v>-13.67998316547284</v>
       </c>
       <c r="F9">
-        <v>-2.711461959147292</v>
+        <v>-3.176310527594121</v>
       </c>
       <c r="G9">
-        <v>-5.923848301548185</v>
+        <v>-6.173996433041055</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-0.8683763510850696</v>
       </c>
       <c r="E10">
-        <v>-15.05040808357007</v>
+        <v>-14.35659605238089</v>
       </c>
       <c r="F10">
-        <v>-2.557048256833073</v>
+        <v>-2.876543504507911</v>
       </c>
       <c r="G10">
-        <v>-6.336560771746967</v>
+        <v>-5.558579259472699</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>0.2450706687447005</v>
       </c>
       <c r="E11">
-        <v>-15.42642992279698</v>
+        <v>-14.66092761959237</v>
       </c>
       <c r="F11">
-        <v>-2.465052363911111</v>
+        <v>-3.221151576883873</v>
       </c>
       <c r="G11">
-        <v>-5.739017233545136</v>
+        <v>-4.93118122159772</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>1.352046148423983</v>
       </c>
       <c r="E12">
-        <v>-15.8606109537044</v>
+        <v>-14.83022009189512</v>
       </c>
       <c r="F12">
-        <v>-2.043404125425639</v>
+        <v>-2.884549137910458</v>
       </c>
       <c r="G12">
-        <v>-5.244805753260576</v>
+        <v>-4.809498809756268</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>2.383349287421667</v>
       </c>
       <c r="E13">
-        <v>-16.43803667442245</v>
+        <v>-16.72083081925345</v>
       </c>
       <c r="F13">
-        <v>-2.108241837456688</v>
+        <v>-2.647911008172538</v>
       </c>
       <c r="G13">
-        <v>-4.120306128845253</v>
+        <v>-4.15447757990161</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>3.263995346584281</v>
       </c>
       <c r="E14">
-        <v>-16.51466298310624</v>
+        <v>-16.49618228068093</v>
       </c>
       <c r="F14">
-        <v>-2.130200711827213</v>
+        <v>-2.282400393271648</v>
       </c>
       <c r="G14">
-        <v>-3.921792576128396</v>
+        <v>-4.014441503590439</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>3.935815802031447</v>
       </c>
       <c r="E15">
-        <v>-17.99589966017117</v>
+        <v>-16.71697255939891</v>
       </c>
       <c r="F15">
-        <v>-1.722341008894515</v>
+        <v>-2.317726537421441</v>
       </c>
       <c r="G15">
-        <v>-3.791876837530777</v>
+        <v>-2.077325439468993</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>4.355518097291598</v>
       </c>
       <c r="E16">
-        <v>-18.29669901765666</v>
+        <v>-18.16859754492768</v>
       </c>
       <c r="F16">
-        <v>-1.193311174518587</v>
+        <v>-2.09030161684659</v>
       </c>
       <c r="G16">
-        <v>-3.530055722466436</v>
+        <v>-2.856988708877211</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>4.501397158992958</v>
       </c>
       <c r="E17">
-        <v>-20.04852560210191</v>
+        <v>-18.32338078650985</v>
       </c>
       <c r="F17">
-        <v>-1.166369961338089</v>
+        <v>-1.535228530544217</v>
       </c>
       <c r="G17">
-        <v>-2.410518605814481</v>
+        <v>-1.622522693283918</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>4.369146795664107</v>
       </c>
       <c r="E18">
-        <v>-20.88617555319673</v>
+        <v>-19.96959882862223</v>
       </c>
       <c r="F18">
-        <v>-0.8289226152587865</v>
+        <v>-1.278340345118531</v>
       </c>
       <c r="G18">
-        <v>-2.059180339368248</v>
+        <v>-1.749445698714036</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>3.970830436911508</v>
       </c>
       <c r="E19">
-        <v>-21.74931628448073</v>
+        <v>-20.84948585678659</v>
       </c>
       <c r="F19">
-        <v>-0.5872498844156846</v>
+        <v>-1.144852149065013</v>
       </c>
       <c r="G19">
-        <v>-1.74265908035853</v>
+        <v>-1.739126728268127</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>3.330586386490235</v>
       </c>
       <c r="E20">
-        <v>-21.37234799418621</v>
+        <v>-21.77543652255697</v>
       </c>
       <c r="F20">
-        <v>-0.2537443823599108</v>
+        <v>-0.4530418940235995</v>
       </c>
       <c r="G20">
-        <v>-2.324225925787839</v>
+        <v>-0.781435561940062</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>2.479774208503355</v>
       </c>
       <c r="E21">
-        <v>-21.76761131947172</v>
+        <v>-21.4616042168774</v>
       </c>
       <c r="F21">
-        <v>0.1668657368979903</v>
+        <v>-0.7024161867334835</v>
       </c>
       <c r="G21">
-        <v>-2.314691554634738</v>
+        <v>-0.7689316314382347</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>1.46051862215107</v>
       </c>
       <c r="E22">
-        <v>-24.19449299576638</v>
+        <v>-21.90924840100962</v>
       </c>
       <c r="F22">
-        <v>0.2880865469305142</v>
+        <v>-0.1601346931101159</v>
       </c>
       <c r="G22">
-        <v>-1.838304051533614</v>
+        <v>-0.4040896497373143</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>0.3121682682806938</v>
       </c>
       <c r="E23">
-        <v>-24.19386806635332</v>
+        <v>-22.6364171717393</v>
       </c>
       <c r="F23">
-        <v>0.8006094145498167</v>
+        <v>-0.07441344302512497</v>
       </c>
       <c r="G23">
-        <v>-2.698837327375148</v>
+        <v>-1.690709999756286</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-0.9118131909003984</v>
       </c>
       <c r="E24">
-        <v>-23.95430726287355</v>
+        <v>-23.54822088470972</v>
       </c>
       <c r="F24">
-        <v>0.5301932131944466</v>
+        <v>0.02646862378836783</v>
       </c>
       <c r="G24">
-        <v>-2.033305115433304</v>
+        <v>-1.269800618802269</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-2.164901301585481</v>
       </c>
       <c r="E25">
-        <v>-24.12711835948026</v>
+        <v>-24.35246428304995</v>
       </c>
       <c r="F25">
-        <v>0.6873744415958962</v>
+        <v>0.08994434873213861</v>
       </c>
       <c r="G25">
-        <v>-2.747770500991115</v>
+        <v>-1.674951802989355</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-3.388623800089391</v>
       </c>
       <c r="E26">
-        <v>-24.41104009433917</v>
+        <v>-23.29346252246021</v>
       </c>
       <c r="F26">
-        <v>0.6418444802329276</v>
+        <v>-0.213382053399021</v>
       </c>
       <c r="G26">
-        <v>-2.926523407384063</v>
+        <v>-1.771086734904251</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.528569542151906</v>
       </c>
       <c r="E27">
-        <v>-24.82030998973039</v>
+        <v>-23.94132865636757</v>
       </c>
       <c r="F27">
-        <v>0.6681514191942922</v>
+        <v>0.03850241318683448</v>
       </c>
       <c r="G27">
-        <v>-2.992390021433403</v>
+        <v>-1.814574061108118</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.535641266546311</v>
       </c>
       <c r="E28">
-        <v>-24.21379788046108</v>
+        <v>-24.29589911422014</v>
       </c>
       <c r="F28">
-        <v>0.6551824514527587</v>
+        <v>-0.05392187218525396</v>
       </c>
       <c r="G28">
-        <v>-3.276792367621112</v>
+        <v>-1.954140039952712</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-6.361477436119062</v>
       </c>
       <c r="E29">
-        <v>-24.01609829070821</v>
+        <v>-24.53377532536906</v>
       </c>
       <c r="F29">
-        <v>0.8643646635876626</v>
+        <v>-0.1144463611556033</v>
       </c>
       <c r="G29">
-        <v>-3.472909085367537</v>
+        <v>-2.269721104029278</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-6.981157922485792</v>
       </c>
       <c r="E30">
-        <v>-23.74795828776604</v>
+        <v>-23.66878697668994</v>
       </c>
       <c r="F30">
-        <v>0.501947818192584</v>
+        <v>-0.3023609865520709</v>
       </c>
       <c r="G30">
-        <v>-3.403778273416476</v>
+        <v>-2.504147454756149</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-7.375698385915316</v>
       </c>
       <c r="E31">
-        <v>-23.62027796311977</v>
+        <v>-23.36945484478293</v>
       </c>
       <c r="F31">
-        <v>0.5864638680759255</v>
+        <v>-0.1866633508996421</v>
       </c>
       <c r="G31">
-        <v>-3.786066830109356</v>
+        <v>-1.884486161806447</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.550100888001423</v>
       </c>
       <c r="E32">
-        <v>-22.4327309393483</v>
+        <v>-22.78390051322111</v>
       </c>
       <c r="F32">
-        <v>0.5199846448635239</v>
+        <v>-0.3778126956283948</v>
       </c>
       <c r="G32">
-        <v>-3.502439151577836</v>
+        <v>-2.188844476504883</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-7.522364542050265</v>
       </c>
       <c r="E33">
-        <v>-22.92124912987375</v>
+        <v>-22.36421512761224</v>
       </c>
       <c r="F33">
-        <v>0.3358724973700263</v>
+        <v>-0.3304868117573178</v>
       </c>
       <c r="G33">
-        <v>-3.732108248364775</v>
+        <v>-2.032047108128381</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-7.32334743155392</v>
       </c>
       <c r="E34">
-        <v>-23.21025634104328</v>
+        <v>-22.92951812341176</v>
       </c>
       <c r="F34">
-        <v>0.1753702376639001</v>
+        <v>-0.7206636462911767</v>
       </c>
       <c r="G34">
-        <v>-3.56819320707884</v>
+        <v>-2.441650976065787</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.99572094891777</v>
       </c>
       <c r="E35">
-        <v>-21.44750707729152</v>
+        <v>-22.2017697080091</v>
       </c>
       <c r="F35">
-        <v>0.07336057223861443</v>
+        <v>-0.7157612846299339</v>
       </c>
       <c r="G35">
-        <v>-2.810124626223288</v>
+        <v>-1.897000023944892</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.58225479069123</v>
       </c>
       <c r="E36">
-        <v>-21.26077545158523</v>
+        <v>-21.66603311900566</v>
       </c>
       <c r="F36">
-        <v>0.1978176853093389</v>
+        <v>-0.4978085091353263</v>
       </c>
       <c r="G36">
-        <v>-2.617073473646228</v>
+        <v>-1.260150378555293</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.124729306668165</v>
       </c>
       <c r="E37">
-        <v>-21.1265016687838</v>
+        <v>-20.6835353983015</v>
       </c>
       <c r="F37">
-        <v>0.02230981205442385</v>
+        <v>-0.5891186573959031</v>
       </c>
       <c r="G37">
-        <v>-2.512152353870106</v>
+        <v>-1.502839850948186</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.660103553167385</v>
       </c>
       <c r="E38">
-        <v>-20.44353080436898</v>
+        <v>-20.13310391114317</v>
       </c>
       <c r="F38">
-        <v>-0.1938343712847519</v>
+        <v>-0.6969460665015556</v>
       </c>
       <c r="G38">
-        <v>-2.47030374770818</v>
+        <v>-2.097956759269731</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.215946090032859</v>
       </c>
       <c r="E39">
-        <v>-20.7132920010059</v>
+        <v>-19.81363818379806</v>
       </c>
       <c r="F39">
-        <v>-0.2522794543881293</v>
+        <v>-0.8147136057854638</v>
       </c>
       <c r="G39">
-        <v>-2.253853659259551</v>
+        <v>-0.5822830739341252</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.812963302271961</v>
       </c>
       <c r="E40">
-        <v>-20.34441156528909</v>
+        <v>-20.31704146838673</v>
       </c>
       <c r="F40">
-        <v>0.04811154882876332</v>
+        <v>-0.6651175368660113</v>
       </c>
       <c r="G40">
-        <v>-1.958188837147241</v>
+        <v>-0.6519468837170088</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.464925069461863</v>
       </c>
       <c r="E41">
-        <v>-18.77555344464975</v>
+        <v>-18.95971742559368</v>
       </c>
       <c r="F41">
-        <v>-0.2269916301833499</v>
+        <v>-0.6511737981335247</v>
       </c>
       <c r="G41">
-        <v>-2.171973936436757</v>
+        <v>-1.388811420393529</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.176828603863168</v>
       </c>
       <c r="E42">
-        <v>-19.26283989024512</v>
+        <v>-18.15074630038945</v>
       </c>
       <c r="F42">
-        <v>0.09006312667579656</v>
+        <v>-1.001476085128449</v>
       </c>
       <c r="G42">
-        <v>-1.871849809483048</v>
+        <v>-1.127966916263274</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.953001326200464</v>
       </c>
       <c r="E43">
-        <v>-18.27175618282241</v>
+        <v>-18.33726961629138</v>
       </c>
       <c r="F43">
-        <v>-0.3422608733856524</v>
+        <v>-0.922188640324931</v>
       </c>
       <c r="G43">
-        <v>-1.75864570476767</v>
+        <v>-1.393446184148509</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.788469822912711</v>
       </c>
       <c r="E44">
-        <v>-18.22402153830756</v>
+        <v>-17.14842744895371</v>
       </c>
       <c r="F44">
-        <v>-0.3208254138201795</v>
+        <v>-0.804985692199877</v>
       </c>
       <c r="G44">
-        <v>-1.154577081307935</v>
+        <v>-1.248649543351865</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.679220301318473</v>
       </c>
       <c r="E45">
-        <v>-17.66926988694592</v>
+        <v>-16.56711176906308</v>
       </c>
       <c r="F45">
-        <v>-0.3127303010334108</v>
+        <v>-0.7278900963833269</v>
       </c>
       <c r="G45">
-        <v>-1.542443907234487</v>
+        <v>-0.983594025295657</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.615758910381331</v>
       </c>
       <c r="E46">
-        <v>-17.38098723161762</v>
+        <v>-16.72818053256789</v>
       </c>
       <c r="F46">
-        <v>-0.4325891239786567</v>
+        <v>-0.5090211470166376</v>
       </c>
       <c r="G46">
-        <v>-1.831633302271982</v>
+        <v>-1.261328932767274</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.588423081862003</v>
       </c>
       <c r="E47">
-        <v>-15.93712857901201</v>
+        <v>-16.54338709373689</v>
       </c>
       <c r="F47">
-        <v>-0.6282156053303567</v>
+        <v>-1.255527061406626</v>
       </c>
       <c r="G47">
-        <v>-2.130340515734882</v>
+        <v>-1.913973190924735</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.589185590223877</v>
       </c>
       <c r="E48">
-        <v>-17.00311324652158</v>
+        <v>-16.36022390554865</v>
       </c>
       <c r="F48">
-        <v>-0.6802807291533863</v>
+        <v>-0.9163320958496359</v>
       </c>
       <c r="G48">
-        <v>-1.432272262233081</v>
+        <v>-0.3058359686772847</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.608937654904265</v>
       </c>
       <c r="E49">
-        <v>-16.44092131236533</v>
+        <v>-14.7171486243976</v>
       </c>
       <c r="F49">
-        <v>-0.7581056215439962</v>
+        <v>-1.079200412193429</v>
       </c>
       <c r="G49">
-        <v>-1.552339127851369</v>
+        <v>-1.141010465688002</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.645621116825939</v>
       </c>
       <c r="E50">
-        <v>-15.73173964039412</v>
+        <v>-13.95276938274689</v>
       </c>
       <c r="F50">
-        <v>-0.8950748031996499</v>
+        <v>-1.253639283955422</v>
       </c>
       <c r="G50">
-        <v>-1.867731490832195</v>
+        <v>-2.159761333942385</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.695478876581511</v>
       </c>
       <c r="E51">
-        <v>-15.13835557727304</v>
+        <v>-14.52731499399606</v>
       </c>
       <c r="F51">
-        <v>-0.6684559889357576</v>
+        <v>-1.14548879884302</v>
       </c>
       <c r="G51">
-        <v>-1.4108364798663</v>
+        <v>-1.310742135486436</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.759104388658707</v>
       </c>
       <c r="E52">
-        <v>-14.55565418433606</v>
+        <v>-13.55174583852363</v>
       </c>
       <c r="F52">
-        <v>-0.910876228970947</v>
+        <v>-0.9720722092494427</v>
       </c>
       <c r="G52">
-        <v>-2.069148391986993</v>
+        <v>-1.008277452836463</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.835587023228329</v>
       </c>
       <c r="E53">
-        <v>-14.57523983441923</v>
+        <v>-13.72106095319642</v>
       </c>
       <c r="F53">
-        <v>-1.099807593565127</v>
+        <v>-1.269815256175721</v>
       </c>
       <c r="G53">
-        <v>-2.234619389676385</v>
+        <v>-1.213541207907894</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.92592371248411</v>
       </c>
       <c r="E54">
-        <v>-13.51600712165509</v>
+        <v>-13.34617123247143</v>
       </c>
       <c r="F54">
-        <v>-1.4927297823034</v>
+        <v>-1.029477589419334</v>
       </c>
       <c r="G54">
-        <v>-2.669214565889749</v>
+        <v>-1.763717460533834</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.029914650931893</v>
       </c>
       <c r="E55">
-        <v>-13.40145031468306</v>
+        <v>-12.5725720177411</v>
       </c>
       <c r="F55">
-        <v>-1.240161946615032</v>
+        <v>-1.343181224561411</v>
       </c>
       <c r="G55">
-        <v>-2.159463384843851</v>
+        <v>-1.251314532510979</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.143606757515771</v>
       </c>
       <c r="E56">
-        <v>-13.48438478765953</v>
+        <v>-11.46793229610205</v>
       </c>
       <c r="F56">
-        <v>-1.193694431350124</v>
+        <v>-1.482641575622051</v>
       </c>
       <c r="G56">
-        <v>-2.103160936857466</v>
+        <v>-1.218295151302288</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.262235437721628</v>
       </c>
       <c r="E57">
-        <v>-13.34183748284609</v>
+        <v>-11.93230919169262</v>
       </c>
       <c r="F57">
-        <v>-0.8759190882994521</v>
+        <v>-1.104317988012298</v>
       </c>
       <c r="G57">
-        <v>-2.755149706998151</v>
+        <v>-1.70332317826091</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.376918428678599</v>
       </c>
       <c r="E58">
-        <v>-12.57488606795902</v>
+        <v>-10.8400276756205</v>
       </c>
       <c r="F58">
-        <v>-1.315830623401771</v>
+        <v>-1.113671355148884</v>
       </c>
       <c r="G58">
-        <v>-3.14666144356344</v>
+        <v>-3.022184931286843</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.479871337705058</v>
       </c>
       <c r="E59">
-        <v>-12.94949955176954</v>
+        <v>-10.96375011398407</v>
       </c>
       <c r="F59">
-        <v>-1.246858647078468</v>
+        <v>-0.917467612991006</v>
       </c>
       <c r="G59">
-        <v>-2.653320636755709</v>
+        <v>-2.616725866364605</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.56159720764021</v>
       </c>
       <c r="E60">
-        <v>-13.29689237831996</v>
+        <v>-10.59833848935713</v>
       </c>
       <c r="F60">
-        <v>-1.507025103749114</v>
+        <v>-1.509251002413264</v>
       </c>
       <c r="G60">
-        <v>-3.096662274283827</v>
+        <v>-2.766345972011966</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.612721141929345</v>
       </c>
       <c r="E61">
-        <v>-12.63709371540239</v>
+        <v>-10.40166233473</v>
       </c>
       <c r="F61">
-        <v>-1.383659164054128</v>
+        <v>-1.047951518922935</v>
       </c>
       <c r="G61">
-        <v>-3.277411439636956</v>
+        <v>-2.563720721735334</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.627434481509433</v>
       </c>
       <c r="E62">
-        <v>-12.50982095341681</v>
+        <v>-11.33514385277514</v>
       </c>
       <c r="F62">
-        <v>-1.49500794326276</v>
+        <v>-1.259890963056619</v>
       </c>
       <c r="G62">
-        <v>-3.367292751028168</v>
+        <v>-2.910308355332713</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.600013787482123</v>
       </c>
       <c r="E63">
-        <v>-12.12942460829849</v>
+        <v>-10.29032980125142</v>
       </c>
       <c r="F63">
-        <v>-1.710993756010392</v>
+        <v>-1.53255365125304</v>
       </c>
       <c r="G63">
-        <v>-2.920739884326956</v>
+        <v>-2.240065237088486</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.52814627799677</v>
       </c>
       <c r="E64">
-        <v>-12.63218937805208</v>
+        <v>-10.36448356312703</v>
       </c>
       <c r="F64">
-        <v>-1.864408139891969</v>
+        <v>-1.648079454813644</v>
       </c>
       <c r="G64">
-        <v>-3.556119647497118</v>
+        <v>-3.328880491136005</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.412416710696318</v>
       </c>
       <c r="E65">
-        <v>-12.42123947335277</v>
+        <v>-10.14429557145207</v>
       </c>
       <c r="F65">
-        <v>-1.559937510236904</v>
+        <v>-1.620423990265283</v>
       </c>
       <c r="G65">
-        <v>-3.04082330267294</v>
+        <v>-2.684840340835109</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.253900234841828</v>
       </c>
       <c r="E66">
-        <v>-12.96610999442968</v>
+        <v>-10.16502239698518</v>
       </c>
       <c r="F66">
-        <v>-1.82707702405323</v>
+        <v>-1.344507578265591</v>
       </c>
       <c r="G66">
-        <v>-3.53557771242594</v>
+        <v>-3.75638447880425</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.058240756491593</v>
       </c>
       <c r="E67">
-        <v>-12.86409706045889</v>
+        <v>-10.28634927259868</v>
       </c>
       <c r="F67">
-        <v>-1.628589577965288</v>
+        <v>-1.599868279335836</v>
       </c>
       <c r="G67">
-        <v>-3.728658659912854</v>
+        <v>-3.773152391960659</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-3.829107341362593</v>
       </c>
       <c r="E68">
-        <v>-12.08175789089375</v>
+        <v>-8.920855862695799</v>
       </c>
       <c r="F68">
-        <v>-1.491044719209373</v>
+        <v>-1.704693773878773</v>
       </c>
       <c r="G68">
-        <v>-3.228802699483837</v>
+        <v>-4.01021393693679</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-3.572671186207332</v>
       </c>
       <c r="E69">
-        <v>-12.24132320102803</v>
+        <v>-9.370320493379106</v>
       </c>
       <c r="F69">
-        <v>-1.70868154537385</v>
+        <v>-2.246504114992298</v>
       </c>
       <c r="G69">
-        <v>-3.373794662467297</v>
+        <v>-4.129661730539234</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-3.295521428639475</v>
       </c>
       <c r="E70">
-        <v>-12.35056810798907</v>
+        <v>-10.18389707664915</v>
       </c>
       <c r="F70">
-        <v>-1.730302298531429</v>
+        <v>-2.401076187898061</v>
       </c>
       <c r="G70">
-        <v>-3.256290159096405</v>
+        <v>-3.508116737177686</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.002657505061817</v>
       </c>
       <c r="E71">
-        <v>-11.39203960020751</v>
+        <v>-9.800489296315728</v>
       </c>
       <c r="F71">
-        <v>-2.166295745198951</v>
+        <v>-1.989129731850571</v>
       </c>
       <c r="G71">
-        <v>-3.036810921479344</v>
+        <v>-4.00957831219325</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-2.702617412379753</v>
       </c>
       <c r="E72">
-        <v>-12.58852130319611</v>
+        <v>-10.71690299582596</v>
       </c>
       <c r="F72">
-        <v>-1.941756336802031</v>
+        <v>-1.710638214032375</v>
       </c>
       <c r="G72">
-        <v>-3.609316803767667</v>
+        <v>-2.90546171666322</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-2.39940022350156</v>
       </c>
       <c r="E73">
-        <v>-11.83316278176868</v>
+        <v>-9.806344613207646</v>
       </c>
       <c r="F73">
-        <v>-2.364336586218739</v>
+        <v>-2.189789230601538</v>
       </c>
       <c r="G73">
-        <v>-3.032272163545003</v>
+        <v>-3.453065675405146</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-2.10119577152522</v>
       </c>
       <c r="E74">
-        <v>-13.39151484271023</v>
+        <v>-10.00366381114387</v>
       </c>
       <c r="F74">
-        <v>-2.18312103684458</v>
+        <v>-2.10774455379924</v>
       </c>
       <c r="G74">
-        <v>-3.616123285396409</v>
+        <v>-3.63669501537744</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-1.814153627981197</v>
       </c>
       <c r="E75">
-        <v>-12.61081950920988</v>
+        <v>-9.659563185197026</v>
       </c>
       <c r="F75">
-        <v>-2.022874545643798</v>
+        <v>-2.382879406929661</v>
       </c>
       <c r="G75">
-        <v>-2.452062641786795</v>
+        <v>-3.060034398437331</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-1.543908569619595</v>
       </c>
       <c r="E76">
-        <v>-13.31186351338932</v>
+        <v>-11.44325211276025</v>
       </c>
       <c r="F76">
-        <v>-2.347645117722965</v>
+        <v>-2.14016143018237</v>
       </c>
       <c r="G76">
-        <v>-2.830173290009115</v>
+        <v>-3.651377284844108</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-1.297839323842971</v>
       </c>
       <c r="E77">
-        <v>-13.91679971370396</v>
+        <v>-12.31293196051132</v>
       </c>
       <c r="F77">
-        <v>-2.634404372272712</v>
+        <v>-2.071145110093434</v>
       </c>
       <c r="G77">
-        <v>-3.027640710335562</v>
+        <v>-3.119842714149804</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-1.078725944398412</v>
       </c>
       <c r="E78">
-        <v>-14.29624960775467</v>
+        <v>-11.25938701110082</v>
       </c>
       <c r="F78">
-        <v>-2.24362810504986</v>
+        <v>-2.244039076734916</v>
       </c>
       <c r="G78">
-        <v>-2.621234829389092</v>
+        <v>-3.291716306912146</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-0.8922137174945542</v>
       </c>
       <c r="E79">
-        <v>-14.36286798888151</v>
+        <v>-11.56485975376223</v>
       </c>
       <c r="F79">
-        <v>-2.71995299841292</v>
+        <v>-2.436589209345875</v>
       </c>
       <c r="G79">
-        <v>-3.359787744290641</v>
+        <v>-2.833675847189664</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-0.7390332448968834</v>
       </c>
       <c r="E80">
-        <v>-15.49661674144186</v>
+        <v>-12.55657744754601</v>
       </c>
       <c r="F80">
-        <v>-2.321210690435407</v>
+        <v>-2.283664190592169</v>
       </c>
       <c r="G80">
-        <v>-3.184537395078242</v>
+        <v>-2.948124717027808</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-0.621779691002079</v>
       </c>
       <c r="E81">
-        <v>-15.85643117219532</v>
+        <v>-13.26445944747702</v>
       </c>
       <c r="F81">
-        <v>-2.642720412034685</v>
+        <v>-2.906106542831419</v>
       </c>
       <c r="G81">
-        <v>-2.605364074073826</v>
+        <v>-2.470316989890337</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-0.5421295587633197</v>
       </c>
       <c r="E82">
-        <v>-16.77194370537802</v>
+        <v>-14.58892941134442</v>
       </c>
       <c r="F82">
-        <v>-2.562881837572594</v>
+        <v>-2.622775219735641</v>
       </c>
       <c r="G82">
-        <v>-2.527999935366598</v>
+        <v>-2.726146017528596</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-0.5006220615512554</v>
       </c>
       <c r="E83">
-        <v>-16.89302604339511</v>
+        <v>-14.93946952733016</v>
       </c>
       <c r="F83">
-        <v>-2.569667225567294</v>
+        <v>-2.392385601687087</v>
       </c>
       <c r="G83">
-        <v>-2.819218694819666</v>
+        <v>-2.28856141869327</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-0.4971256527081879</v>
       </c>
       <c r="E84">
-        <v>-18.25351548951951</v>
+        <v>-15.42395284751479</v>
       </c>
       <c r="F84">
-        <v>-2.465765031573058</v>
+        <v>-2.828015587847016</v>
       </c>
       <c r="G84">
-        <v>-2.172149395350338</v>
+        <v>-2.2125678458393</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-0.5281322062321513</v>
       </c>
       <c r="E85">
-        <v>-19.53519137401443</v>
+        <v>-18.21015535089607</v>
       </c>
       <c r="F85">
-        <v>-2.917540107687934</v>
+        <v>-2.338346388440462</v>
       </c>
       <c r="G85">
-        <v>-2.47920580466328</v>
+        <v>-2.059392214282761</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.5903630506136582</v>
       </c>
       <c r="E86">
-        <v>-20.37894570807158</v>
+        <v>-18.18805186926463</v>
       </c>
       <c r="F86">
-        <v>-2.674096793631371</v>
+        <v>-2.847185556100452</v>
       </c>
       <c r="G86">
-        <v>-2.228107546600639</v>
+        <v>-2.317843193988124</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.6783262104457669</v>
       </c>
       <c r="E87">
-        <v>-20.73504679013875</v>
+        <v>-20.4347500932681</v>
       </c>
       <c r="F87">
-        <v>-2.893267438974952</v>
+        <v>-2.94299263730792</v>
       </c>
       <c r="G87">
-        <v>-2.351190319205202</v>
+        <v>-2.05235730501181</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.7870739112245022</v>
       </c>
       <c r="E88">
-        <v>-22.55125468955105</v>
+        <v>-20.01010602862084</v>
       </c>
       <c r="F88">
-        <v>-2.778507357224463</v>
+        <v>-2.637171106506985</v>
       </c>
       <c r="G88">
-        <v>-1.587417668385486</v>
+        <v>-2.046812141233531</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.9100975206971017</v>
       </c>
       <c r="E89">
-        <v>-24.6037040209955</v>
+        <v>-21.61683124891232</v>
       </c>
       <c r="F89">
-        <v>-2.930771178758473</v>
+        <v>-2.779568440187808</v>
       </c>
       <c r="G89">
-        <v>-1.728023158529412</v>
+        <v>-1.695275242054941</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-1.041713119037768</v>
       </c>
       <c r="E90">
-        <v>-25.41274307330986</v>
+        <v>-22.72191476100412</v>
       </c>
       <c r="F90">
-        <v>-2.675810363431877</v>
+        <v>-2.935445486767893</v>
       </c>
       <c r="G90">
-        <v>-1.371295323945245</v>
+        <v>-1.762141640857141</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.175812965312412</v>
       </c>
       <c r="E91">
-        <v>-28.75998274997544</v>
+        <v>-26.94991998979154</v>
       </c>
       <c r="F91">
-        <v>-2.96340106358723</v>
+        <v>-2.815349899788289</v>
       </c>
       <c r="G91">
-        <v>-1.933823221978205</v>
+        <v>-1.828498215646292</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-1.307175863647402</v>
       </c>
       <c r="E92">
-        <v>-29.53853837950716</v>
+        <v>-28.73743094941724</v>
       </c>
       <c r="F92">
-        <v>-2.926128544867363</v>
+        <v>-2.735311778380852</v>
       </c>
       <c r="G92">
-        <v>-2.189483411793962</v>
+        <v>-1.803500286279256</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-1.432675315111059</v>
       </c>
       <c r="E93">
-        <v>-32.22262605825248</v>
+        <v>-29.83431113084414</v>
       </c>
       <c r="F93">
-        <v>-3.109362527430749</v>
+        <v>-3.089716655549723</v>
       </c>
       <c r="G93">
-        <v>-2.124153106121984</v>
+        <v>-1.581213706044892</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-1.548758805202084</v>
       </c>
       <c r="E94">
-        <v>-34.36682453732934</v>
+        <v>-31.83567701124507</v>
       </c>
       <c r="F94">
-        <v>-3.070477004236007</v>
+        <v>-3.250928415505966</v>
       </c>
       <c r="G94">
-        <v>-2.467734764369705</v>
+        <v>-2.11458894005903</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-1.65507689129501</v>
       </c>
       <c r="E95">
-        <v>-35.82920691286333</v>
+        <v>-33.54156449111951</v>
       </c>
       <c r="F95">
-        <v>-2.931315181740427</v>
+        <v>-3.240941566003205</v>
       </c>
       <c r="G95">
-        <v>-2.733518602444553</v>
+        <v>-1.648189352849887</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-1.748600831180094</v>
       </c>
       <c r="E96">
-        <v>-38.38336361538058</v>
+        <v>-35.36330392153219</v>
       </c>
       <c r="F96">
-        <v>-3.062053272471784</v>
+        <v>-3.001651520709881</v>
       </c>
       <c r="G96">
-        <v>-2.461894962038431</v>
+        <v>-2.468572332391141</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-1.828825337365974</v>
       </c>
       <c r="E97">
-        <v>-41.09688184670176</v>
+        <v>-38.13055249695437</v>
       </c>
       <c r="F97">
-        <v>-3.345033804707293</v>
+        <v>-3.520669166288401</v>
       </c>
       <c r="G97">
-        <v>-3.526030099090682</v>
+        <v>-3.448692444747768</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-1.890269642272869</v>
       </c>
       <c r="E98">
-        <v>-43.00848884379664</v>
+        <v>-40.45760396374994</v>
       </c>
       <c r="F98">
-        <v>-3.170202965731229</v>
+        <v>-3.439647563507477</v>
       </c>
       <c r="G98">
-        <v>-3.338292372104153</v>
+        <v>-2.808088640716636</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-1.930706900495495</v>
       </c>
       <c r="E99">
-        <v>-45.14001891683704</v>
+        <v>-44.60341965353515</v>
       </c>
       <c r="F99">
-        <v>-3.313207650630622</v>
+        <v>-3.457319345964908</v>
       </c>
       <c r="G99">
-        <v>-3.809108227062683</v>
+        <v>-3.725953944207269</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-1.937547945377629</v>
       </c>
       <c r="E100">
-        <v>-47.82030267741592</v>
+        <v>-46.43651423252206</v>
       </c>
       <c r="F100">
-        <v>-3.407496749718141</v>
+        <v>-3.604562819746975</v>
       </c>
       <c r="G100">
-        <v>-3.768759298030046</v>
+        <v>-4.234543123768884</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-1.910820745105431</v>
       </c>
       <c r="E101">
-        <v>-49.5423251101797</v>
+        <v>-47.6393312706474</v>
       </c>
       <c r="F101">
-        <v>-3.191261503288827</v>
+        <v>-3.706468752434799</v>
       </c>
       <c r="G101">
-        <v>-4.628723160038826</v>
+        <v>-3.49778783509516</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-1.826670781806888</v>
       </c>
       <c r="E102">
-        <v>-51.75348047381546</v>
+        <v>-49.82434941442939</v>
       </c>
       <c r="F102">
-        <v>-3.657209163640971</v>
+        <v>-3.489524797608327</v>
       </c>
       <c r="G102">
-        <v>-4.385613248362446</v>
+        <v>-3.927615825731974</v>
       </c>
     </row>
   </sheetData>
